--- a/03_dq_report.xlsx
+++ b/03_dq_report.xlsx
@@ -4,13 +4,12 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary Scorecard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Defect Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reconciliation Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">AstraPay Data Quality Scorecard — measured on the Jan–Jun 2025 extract (10 source files, 56,829 total rows profiled)</t>
   </si>
@@ -79,7 +78,7 @@
     <t xml:space="preserve">Pass — 0 dup transaction_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Watch — 0.51% success w/ a Decline on file</t>
+    <t xml:space="preserve">Watch — 0.51% success w/ a Decline on Fraud Detection  file</t>
   </si>
   <si>
     <t xml:space="preserve">Fail — 3.79% success w/o settlement</t>
@@ -692,36 +691,6 @@
   </si>
   <si>
     <t xml:space="preserve">Looks close to baseline — but this NETS two offsetting errors: 352 transactions double-counted (+704 rows) against 267 successful transactions dropped entirely (-875 combined with the join's exclusion of all non-successful statuses). A small net delta here is not evidence of correctness.</t>
-  </si>
-  <si>
-    <t>Methodology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All counts, percentages, and reconciliation figures in this workbook are measured directly by a Python (pandas) profiling script run once against the full six-month extract (10 CSVs, 56,829 total rows, 2025-01-01 to 2025-06-30). They are point-in-time findings, not live spreadsheet formulas — the source data (tens of thousands of transaction-grain rows) is not embedded in this workbook.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checks performed per dataset: null/blank counts on critical fields (completeness); domain-membership and range checks against the values documented in the case brief and the Data Contract (validity); primary/natural-key duplicate checks (uniqueness); cross-field and cross-table logical checks — e.g. sign of amount vs. status, fraud decision vs. transaction outcome, risk_score vs. risk_band (consistency); event_time vs. ingestion_time gaps and route/period latency segmentation (timeliness); transaction-to-settlement coverage and join fan-out tests using row counts and SUM(amount) before/after a join (reconciliation).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severity definitions used throughout the Defect Log:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blocking — will silently corrupt a required KPI or Task deliverable if not explicitly handled (e.g. inflates GPV, breaks a segmentation cut, misstates settlement coverage).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Warning — needs a documented handling rule but has a contained, quantifiable impact if that rule is followed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Informational — worth knowing; not a pipeline defect, or a business question rather than a data-engineering one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pass — checked and found clean; included so dimensions are not silently skipped just because nothing was wrong.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remediation vocabulary (per the case brief) for every Blocking item: Exclude (drop from a specific calculation), Repair (deterministically correct or re-derive the value/record), Quarantine (set aside from analysis pending investigation, not silently dropped from the dataset), or Retain with a flag (keep in the base data, carry an explicit indicator column so every downstream query can choose how to treat it).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: generate_astrapay_data.py (seed=42) and the resulting 10 CSVs, as delivered with the dataset README. Re-running the profiling script against the same files reproduces every figure in this workbook exactly.</t>
   </si>
 </sst>
 </file>
@@ -782,7 +751,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -817,6 +786,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
         <bgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -860,7 +835,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -891,6 +866,10 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="5" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="5" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -928,7 +907,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="1" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="1" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -940,14 +919,6 @@
     </xf>
     <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -1594,8 +1565,8 @@
       <c r="E8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>19</v>
+      <c r="F8" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>13</v>
@@ -1735,24 +1706,24 @@
       </c>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" ht="15">
-      <c r="A17" s="14"/>
+      <c r="A17" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1814,553 +1785,553 @@
       </c>
     </row>
     <row r="2" ht="67.5" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" ht="67.5" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" ht="67.5" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" ht="67.5" customHeight="1">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="16" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" ht="67.5" customHeight="1">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" ht="67.5" customHeight="1">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="9" ht="67.5" customHeight="1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="16" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="10" ht="67.5" customHeight="1">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="16" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="11" ht="67.5" customHeight="1">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="12" ht="67.5" customHeight="1">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="16" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="14" ht="67.5" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="15" ht="67.5" customHeight="1">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" ht="67.5" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="18" ht="67.5" customHeight="1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="16" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2387,15 +2358,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2411,62 +2382,62 @@
       </c>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>7040</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>653</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" ht="15">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="16">
         <v>157</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" ht="15">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <v>150</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" ht="15">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <v>8000</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="23" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="11" ht="15">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>194</v>
       </c>
     </row>
@@ -2482,84 +2453,84 @@
       </c>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="16">
         <v>7040</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="14" ht="23.850000000000001">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="16">
         <v>35</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" ht="23.850000000000001">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="23">
         <v>7005</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="23" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="16" ht="15">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="16">
         <v>6421</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="17" ht="23.850000000000001">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <v>352</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="18" ht="15">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <v>232</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="19" ht="23.850000000000001">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="16">
         <v>71</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="21" ht="15">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2578,44 +2549,44 @@
       </c>
     </row>
     <row r="23" ht="45.75" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="16" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="24" ht="45.75" customHeight="1">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="16" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="16" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2628,86 +2599,4 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="136.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75">
-      <c r="A1" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23"/>
-    </row>
-    <row r="3" ht="21" customHeight="1"/>
-    <row r="4" ht="46.5" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" ht="62.5" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="23" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="23"/>
-    </row>
-    <row r="13" ht="45.5" customHeight="1">
-      <c r="A13" s="23" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>233</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.29999999999999999" right="0.29999999999999999" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-</worksheet>
 </file>